--- a/gaming_forms/041_runeheim_character_submission--gaming_forms.xlsx
+++ b/gaming_forms/041_runeheim_character_submission--gaming_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>halfling</t>
+          <t>human</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Halfling</t>
+          <t>Human</t>
         </is>
       </c>
     </row>
@@ -1233,29 +1233,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>tiefling</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Tiefling</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>character_race_type_choices</t>
+          <t>character_class_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>tiefling</t>
+          <t>barbarian</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tiefling</t>
+          <t>Barbarian</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>barbarian</t>
+          <t>bard</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Barbarian</t>
+          <t>Bard</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>bard</t>
+          <t>cleric</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bard</t>
+          <t>Cleric</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>cleric</t>
+          <t>druid</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cleric</t>
+          <t>Druid</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>druid</t>
+          <t>fighter</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Druid</t>
+          <t>Fighter</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fighter</t>
+          <t>monk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fighter</t>
+          <t>Monk</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>monk</t>
+          <t>paladin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Monk</t>
+          <t>Paladin</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>paladin</t>
+          <t>ranger</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Paladin</t>
+          <t>Ranger</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>rogue</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ranger</t>
+          <t>Rogue</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rogue</t>
+          <t>sorcerer</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rogue</t>
+          <t>Sorcerer</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sorcerer</t>
+          <t>warlock</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sorcerer</t>
+          <t>Warlock</t>
         </is>
       </c>
     </row>
@@ -1437,29 +1437,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>warlock</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Warlock</t>
+          <t>Wizard</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>character_class_type_choices</t>
+          <t>character_background_type_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>acolyte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wizard</t>
+          <t>Acolyte</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>acolyte</t>
+          <t>aristocrat</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Acolyte</t>
+          <t>Aristocrat</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>aristocrat</t>
+          <t>entertainer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Aristocrat</t>
+          <t>Entertainer</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>entertainer</t>
+          <t>folk_hero</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Entertainer</t>
+          <t>Folk Hero</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>folk_hero</t>
+          <t>guild_member</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Folk Hero</t>
+          <t>Guild Member</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>guild_member</t>
+          <t>knight_of_the_order_of_saren</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Guild Member</t>
+          <t>Knight of the Order of Saren</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>knight_of_the_order_of_saren</t>
+          <t>noble</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Knight of the Order of Saren</t>
+          <t>Noble</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>noble</t>
+          <t>outlander</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Noble</t>
+          <t>Outlander</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>outlander</t>
+          <t>outlander_(npc)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Outlander</t>
+          <t>Outlander (NPC)</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>outlander_(npc)</t>
+          <t>pirate</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Outlander (NPC)</t>
+          <t>Pirate</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>pirate</t>
+          <t>sage</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pirate</t>
+          <t>Sage</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sage</t>
+          <t>soldier</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sage</t>
+          <t>Soldier</t>
         </is>
       </c>
     </row>
@@ -1658,29 +1658,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>soldier</t>
+          <t>urchin</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>Urchin</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>character_background_type_choices</t>
+          <t>character_proficiency_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>urchin</t>
+          <t>acrobatics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Urchin</t>
+          <t>Acrobatics</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>acrobatics</t>
+          <t>athletics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Acrobatics</t>
+          <t>Athletics</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>athletics</t>
+          <t>stealth</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Stealth</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>stealth</t>
+          <t>perception</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Stealth</t>
+          <t>Perception</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>perception</t>
+          <t>persuasion</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>Persuasion</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>persuasion</t>
+          <t>deception</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Persuasion</t>
+          <t>Deception</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>deception</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Deception</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>arcana</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Arcana</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>arcana</t>
+          <t>insight</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arcana</t>
+          <t>Insight</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>insight</t>
+          <t>intimidation</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Intimidation</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>intimidation</t>
+          <t>medicine</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Intimidation</t>
+          <t>Medicine</t>
         </is>
       </c>
     </row>
@@ -1862,129 +1862,44 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>athletics</t>
+          <t>sleight_of_hand</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Sleight of Hand</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>character_proficiency_choices</t>
+          <t>character_location_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>acrobatics</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Acrobatics</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>character_proficiency_choices</t>
+          <t>character_location_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>medicine</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
-        <is>
-          <t>Medicine</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>character_proficiency_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>sleight_of_hand</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Sleight of Hand</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>character_proficiency_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>persuasion</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Persuasion</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>character_proficiency_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>deception</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Deception</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>character_location_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>character_location_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
         <is>
           <t>No</t>
         </is>
